--- a/artfynd/A 73869-2021 artfynd.xlsx
+++ b/artfynd/A 73869-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 73869-2021 artfynd.xlsx
+++ b/artfynd/A 73869-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY112"/>
+  <dimension ref="A1:AZ112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101786284</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101729715</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -969,6 +984,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101730797</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1067,6 +1087,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101729464</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1165,6 +1190,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101730262</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1266,6 +1296,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101731234</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1364,6 +1399,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101731968</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1462,6 +1502,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101731762</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1560,6 +1605,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101732040</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1658,6 +1708,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101729362</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1756,6 +1811,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101730492</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1854,6 +1914,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101731833</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1952,6 +2017,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101729526</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2050,6 +2120,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101731266</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2151,6 +2226,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101786614</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2249,6 +2329,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101729974</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2347,6 +2432,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101731321</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2445,6 +2535,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101729157</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2543,6 +2638,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101729284</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2641,6 +2741,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101729497</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2739,6 +2844,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101729645</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2837,6 +2947,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101729693</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2935,6 +3050,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101729774</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3033,6 +3153,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101729812</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3131,6 +3256,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101729834</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3229,6 +3359,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101730085</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3327,6 +3462,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101730137</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3425,6 +3565,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101730300</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3523,6 +3668,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101730340</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3621,6 +3771,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101730423</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3719,6 +3874,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101730531</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3817,6 +3977,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101730608</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3915,6 +4080,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101730753</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4013,6 +4183,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101730800</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4111,6 +4286,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101730844</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4209,6 +4389,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101730901</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4307,6 +4492,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101730943</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4405,6 +4595,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101731223</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4503,6 +4698,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101731357</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4601,6 +4801,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101731404</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4699,6 +4904,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101731479</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4797,6 +5007,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101731706</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4895,6 +5110,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101731756</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4993,6 +5213,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101731786</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5091,6 +5316,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101731886</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5189,6 +5419,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101731967</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5287,6 +5522,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101731538</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5385,6 +5625,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101731866</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5483,6 +5728,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101729820</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5581,6 +5831,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101730428</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5679,6 +5934,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101731506</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5777,6 +6037,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101731860</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5886,6 +6151,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101731430</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6002,6 +6272,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101731108</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6111,6 +6386,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101731566</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6220,6 +6500,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101731883</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6319,6 +6604,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101729422</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6418,6 +6708,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101729765</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6517,6 +6812,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101729847</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6616,6 +6916,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101730061</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6715,6 +7020,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101730819</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6814,6 +7124,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101731164</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6912,6 +7227,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101730569</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7010,6 +7330,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101731864</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7108,6 +7433,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101741099</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7206,6 +7536,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101741123</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7304,6 +7639,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101741411</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7402,6 +7742,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101741004</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7500,6 +7845,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101741007</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7598,6 +7948,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101741052</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7696,6 +8051,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101741221</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7794,6 +8154,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101741532</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7892,6 +8257,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101742163</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7990,6 +8360,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101741110</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8088,6 +8463,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101741346</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8186,6 +8566,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101742149</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8284,6 +8669,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101740961</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8382,6 +8772,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101741505</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8494,6 +8889,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/437508</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8592,6 +8992,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101742161</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8704,6 +9109,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1727366</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8802,6 +9212,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101740899</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8900,6 +9315,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101741050</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8998,6 +9418,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101741088</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9096,6 +9521,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101741162</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9194,6 +9624,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101741250</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9292,6 +9727,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101741303</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9390,6 +9830,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101741446</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9488,6 +9933,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101741489</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9586,6 +10036,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101741546</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9684,6 +10139,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101741694</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9782,6 +10242,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101741724</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9880,6 +10345,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101741796</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9978,6 +10448,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101741847</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10076,6 +10551,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101741920</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10174,6 +10654,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101741970</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10272,6 +10757,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101742060</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10370,6 +10860,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101742117</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10468,6 +10963,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101742183</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10566,6 +11066,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101741862</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10664,6 +11169,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101741070</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10762,6 +11272,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101741295</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10874,6 +11389,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2090108</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -10972,6 +11492,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101741854</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11070,6 +11595,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101742085</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11174,6 +11704,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101741611</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11284,6 +11819,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101742091</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11393,6 +11933,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101742172</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11492,6 +12037,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101741153</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11591,6 +12141,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101741365</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11689,8 +12244,126 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101741857</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>